--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July 2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August 2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="October 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="November 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="December 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January 2026" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February 2026" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="April 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="May 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="June 2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="July 2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="August 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="September 2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="October 2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="November 2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="December 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="January 2027" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="February 2027" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="March 2027" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>July 2025</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,495 +612,40 @@
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>1
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>2
-Kati - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>3
-Kati - Day
-Megan - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>4
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>5
-David - Day
-Megan - Day
-Ashley - Night
-Template Week 1 - Dr. Amin</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>6
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>7
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>8
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>9
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>10
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>11
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>12
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 2</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>13
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>14
-Britt - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>15
-Britt - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>16
-Kati - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>17
-Kati - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>18
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>19
-David - Day
-None - Day
-None - Night
-Template Week 3 - Dr. Amin</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>20
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>21
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>22
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>23
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>24
-David - Day
-None - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>25
-Britt - Day
-Kati - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>26
-Britt - Day
-Kati - Day
-Ashley - Night
-Template Week 4</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>27
-Britt - Day
-Kati - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>28
-Britt - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>29
-Britt - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>30
-Kati - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>31
-Kati - Day
-David - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A1:N2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K3:L3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="3" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="6" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="N3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="9" t="inlineStr">
         <is>
           <t>1
 David - Day
-None - Day
-None - Night</t>
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>2
-David - Day
-None - Day
-None - Night</t>
+David  - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>3
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>4
-Britt - Day
-Kati - Day
-Ashley - Night
-Template Week 4 - Dr. Amin</t>
+David - Day
+Liz - Night
+Template Week 13 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -1109,64 +654,62 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>5
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>6
-Britt - Day
-None - Day
-Liz - Night</t>
+David - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>7
-Britt - Day
-None - Day
-Liz - Night</t>
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>8
-Kati - Day
-None - Day
-Ashley - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>9
-Kati - Day
-David - Day
-Ashley - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
           <t>10
-David - Day
-Megan - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>11
-David - Day
-Megan - Day
-Liz - Night
-Template Week 5</t>
+Megan - Day
+Britt - Day
+Ashley - Night
+Template Week 14</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -1175,18 +718,18 @@
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>12
-David - Day
-Megan - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>13
-Britt - Day
-None - Day
-Ashley - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
@@ -1194,45 +737,42 @@
         <is>
           <t>14
 Britt - Day
-None - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>15
-Megan - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>16
-Megan - Day
-David - Day
-Liz - Night</t>
+David - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>17
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+David  - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
           <t>18
-Britt - Day
-Kati - Day
-Ashley - Night
-Template Week 6 - Dr. Amin</t>
+David  - Day
+Josh - Night
+Template Week 1 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -1241,17 +781,16 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>19
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>20
-Megan - Day
-None - Day
+David - Day
+Britt  - Day
 Liz - Night</t>
         </is>
       </c>
@@ -1259,8 +798,7 @@
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>21
-Megan - Day
-None - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -1268,8 +806,8 @@
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>22
-Kati - Day
-Megan - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1277,8 +815,8 @@
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>23
-Kati - Day
-None - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1286,8 +824,8 @@
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>24
-David - Day
-None - Day
+Megan - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -1295,10 +833,10 @@
       <c r="M7" s="9" t="inlineStr">
         <is>
           <t>25
-David - Day
-None - Day
+Megan - Day
+Britt - Day
 Liz - Night
-Template Week 7</t>
+Template Week 2</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -1307,8 +845,8 @@
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>26
-David - Day
-None - Day
+Megan - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -1316,8 +854,8 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>27
-Britt - Day
-None - Day
+Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1326,7 +864,6 @@
         <is>
           <t>28
 Britt - Day
-None - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1334,17 +871,15 @@
       <c r="G8" s="9" t="inlineStr">
         <is>
           <t>29
-David - Day
-None - Day
-Ashley - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>30
-David - Day
-None - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -1400,7 +935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1428,7 +963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1519,19 +1054,19 @@
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>1
-Britt - Day
-Kati - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>2
-Britt - Day
-Kati - Day
-None - Night
-Template Week 8 - Dr. Amin</t>
+Megan - Day
+Josh - Day
+Britt - Night
+Template Week 10 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -1540,17 +1075,17 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>3
-Britt - Day
-Kati - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>4
-David - Day
-Britt - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1559,7 +1094,6 @@
         <is>
           <t>5
 David - Day
-None - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1567,18 +1101,16 @@
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>6
-Kati - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>7
-Kati - Day
-Megan - Day
-Liz - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
@@ -1586,8 +1118,7 @@
         <is>
           <t>8
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
@@ -1595,9 +1126,8 @@
         <is>
           <t>9
 David - Day
-None - Day
-Ashley - Night
-Template Week 9</t>
+Liz - Night
+Template Week 11</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -1607,17 +1137,16 @@
         <is>
           <t>10
 David - Day
-None - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>11
-Britt - Day
-None - Day
-Liz - Night</t>
+David - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
@@ -1625,45 +1154,43 @@
         <is>
           <t>12
 Britt - Day
-Megan - Day
-Liz - Night</t>
+Ashley - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>13
-David - Day
-Megan - Day
-Ashley - Night</t>
+Megan - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>14
-David - Day
-Megan - Day
-Ashley - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>15
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
           <t>16
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 10 - Dr. Amin</t>
+Megan - Day
+Josh  - Day
+Ashley - Night
+Template Week 12 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -1672,45 +1199,44 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>17
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>18
-David - Day
-Megan - Day
-Ashley - Night</t>
+Megan - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>19
-David - Day
-Megan - Day
-Ashley - Night</t>
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>20
-Kati - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>21
-Kati - Day
-None - Day
-Liz - Night</t>
+David  - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
@@ -1718,8 +1244,7 @@
         <is>
           <t>22
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
@@ -1727,9 +1252,8 @@
         <is>
           <t>23
 David - Day
-Megan - Day
-Ashley - Night
-Template Week 11</t>
+Liz - Night
+Template Week 13</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -1739,26 +1263,24 @@
         <is>
           <t>24
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>25
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
           <t>26
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -1766,8 +1288,8 @@
         <is>
           <t>27
 Megan - Day
-David - Day
-Ashley - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
@@ -1775,27 +1297,27 @@
         <is>
           <t>28
 Megan - Day
-David - Day
-Ashley - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
           <t>29
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="9" t="inlineStr">
         <is>
           <t>30
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 12 - Dr. Amin</t>
+Megan - Day
+Britt - Day
+Ashley - Night
+Template Week 14 - Dr. Amin</t>
         </is>
       </c>
       <c r="N8" s="8" t="n"/>
@@ -1804,9 +1326,9 @@
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>31
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -1870,6 +1392,422 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>1
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>2
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>3
+David - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>4
+David - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>5
+David  - Day
+Britt - Night</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>6
+David  - Day
+Josh - Night
+Template Week 1 - Dr. Amin</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>7
+David - Day
+Josh - Night</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>8
+David - Day
+Britt  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>9
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>10
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>11
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>12
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>13
+Megan - Day
+Britt - Day
+Liz - Night
+Template Week 2</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>14
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>15
+Megan - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>16
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>17
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>18
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>19
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>20
+Josh - Day
+Ashley - Night
+Template Week 3 - Dr. Amin</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>21
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>22
+Josh - Day
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>23
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>24
+Megan - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>25
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>26
+Megan - Day
+Josh - Day
+David  - Night</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>27
+Megan - Day
+Josh - Day
+David  - Night
+Template Week 4</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>28
+Megan - Day
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K3:L3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1898,7 +1836,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1981,17 +1919,16 @@
       <c r="C4" s="9" t="inlineStr">
         <is>
           <t>1
-Britt - Day
-David - Day
-Ashley - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
           <t>2
-David - Day
-None - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -1999,18 +1936,18 @@
       <c r="G4" s="9" t="inlineStr">
         <is>
           <t>3
-Kati - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>4
-Kati - Day
-Megan - Day
-Liz - Night</t>
+David  - Day
+Josh  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
@@ -2018,8 +1955,7 @@
         <is>
           <t>5
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
@@ -2027,9 +1963,8 @@
         <is>
           <t>6
 David - Day
-Megan - Day
-Ashley - Night
-Template Week 1 - Dr. Amin</t>
+Liz - Night
+Template Week 5 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -2038,18 +1973,17 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>7
-David - Day
-Megan - Day
-Ashley - Night</t>
+David  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>8
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David  - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
@@ -2057,45 +1991,44 @@
         <is>
           <t>9
 Britt - Day
-Kati - Day
-Liz - Night</t>
+Ashley - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>10
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>11
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
           <t>12
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>13
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 2</t>
+Megan - Day
+Britt  - Day
+Ashley - Night
+Template Week 6</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -2104,35 +2037,33 @@
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>14
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>15
-Britt - Day
-None - Day
-None - Night</t>
+Megan - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>16
-Britt - Day
-None - Day
-None - Night</t>
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>17
-Kati - Day
-None - Day
+David - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -2140,8 +2071,8 @@
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>18
-Kati - Day
-None - Day
+David  - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -2149,9 +2080,8 @@
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>19
-David - Day
-None - Day
-None - Night</t>
+David  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
@@ -2159,9 +2089,8 @@
         <is>
           <t>20
 David - Day
-None - Day
-None - Night
-Template Week 3 - Dr. Amin</t>
+Liz - Night
+Template Week 7 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -2171,63 +2100,59 @@
         <is>
           <t>21
 David - Day
-None - Day
-None - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>22
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David - Day
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>23
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>24
-David - Day
-None - Day
-None - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>25
-David - Day
-None - Day
-None - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>26
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+Josh - Day
+Britt - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="9" t="inlineStr">
         <is>
           <t>27
-Britt - Day
-Kati - Day
-Ashley - Night
-Template Week 4</t>
+Josh - Day
+Britt  - Day
+Megan - Night
+Template Week 8</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -2236,8 +2161,8 @@
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>28
-Britt - Day
-Kati - Day
+Josh - Day
+Britt  - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -2245,9 +2170,9 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>29
-Britt - Day
-None - Day
-Liz - Night</t>
+Josh - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -2255,12 +2180,17 @@
         <is>
           <t>30
 Britt - Day
-None - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>31
+David - Day
+Liz - Night</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
@@ -2270,13 +2200,14 @@
       <c r="N8" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
@@ -2343,7 +2274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>August 2025</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2434,285 +2365,271 @@
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>1
-David - Day
-Megan - Day
-Liz - Night</t>
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>2
-David - Day
-Megan - Day
+Josh - Day
+Ashley - Night
+Template Week 3 - Dr. Amin</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>3
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>4
+Josh - Day
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>5
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>6
+Megan - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>7
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>8
+Megan - Day
+Josh - Day
+David  - Night</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>9
+Megan - Day
+Josh - Day
+David  - Night
+Template Week 4</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>10
+Megan - Day
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>11
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>12
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>13
+David - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>14
+David  - Day
+Josh  - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>15
+David - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>16
+David - Day
 Liz - Night
 Template Week 5 - Dr. Amin</t>
         </is>
       </c>
-      <c r="N4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>3
-David - Day
-Megan - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>4
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>5
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>6
-Megan - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>7
-Megan - Day
-David - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>8
-Britt - Day
-Kati - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>9
-Britt - Day
-Kati - Day
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>17
+David  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>18
+David  - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>19
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>20
+Megan - Day
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>21
+Megan - Day
+Josh  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>22
+Megan - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>23
+Megan - Day
+Britt  - Day
 Ashley - Night
 Template Week 6</t>
         </is>
       </c>
-      <c r="N5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>10
-Britt - Day
-Kati - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>11
-Megan - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>12
-Megan - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>13
-Kati - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>14
-Kati - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>15
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>16
-David - Day
-None - Day
+      <c r="N7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>24
+Megan - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>25
+Megan - Day
+Britt  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>26
+Britt  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>27
+David - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>28
+David  - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>29
+David  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>30
+David - Day
 Liz - Night
 Template Week 7 - Dr. Amin</t>
         </is>
       </c>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>17
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>18
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>19
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>20
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>21
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>22
-Britt - Day
-Kati - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>23
-Britt - Day
-Kati - Day
-None - Night
-Template Week 8</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>24
-Britt - Day
-Kati - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>25
-David - Day
-Britt - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>26
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>27
-Kati - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>28
-Kati - Day
-Megan - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>29
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>30
-David - Day
-None - Day
-Ashley - Night
-Template Week 9 - Dr. Amin</t>
-        </is>
-      </c>
       <c r="N8" s="8" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -2720,8 +2637,7 @@
         <is>
           <t>31
 David - Day
-None - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -2813,7 +2729,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>September 2025</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2896,55 +2812,52 @@
       <c r="C4" s="9" t="inlineStr">
         <is>
           <t>1
-Britt - Day
-None - Day
-Liz - Night</t>
+David - Day
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
           <t>2
-Britt - Day
-Megan - Day
-Liz - Night</t>
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="9" t="inlineStr">
         <is>
           <t>3
-David - Day
-Megan - Day
-Ashley - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>4
-David - Day
-Megan - Day
-Ashley - Night</t>
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>5
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Josh - Day
+Britt - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>6
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 10 - Dr. Amin</t>
+Josh - Day
+Britt  - Day
+Megan - Night
+Template Week 8 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -2953,17 +2866,17 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>7
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Josh - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>8
-David - Day
-Megan - Day
+Josh - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -2971,17 +2884,15 @@
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>9
-David - Day
-Megan - Day
-Ashley - Night</t>
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>10
-Kati - Day
-None - Day
+David - Day
 Liz - Night</t>
         </is>
       </c>
@@ -2989,8 +2900,7 @@
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>11
-Kati - Day
-None - Day
+David - Day
 Liz - Night</t>
         </is>
       </c>
@@ -2999,7 +2909,6 @@
         <is>
           <t>12
 David - Day
-Megan - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3008,9 +2917,8 @@
         <is>
           <t>13
 David - Day
-Megan - Day
 Ashley - Night
-Template Week 11</t>
+Template Week 9</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -3020,7 +2928,6 @@
         <is>
           <t>14
 David - Day
-Megan - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3028,8 +2935,8 @@
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>15
-Britt - Day
-Kati - Day
+David - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -3038,7 +2945,6 @@
         <is>
           <t>16
 Britt - Day
-Kati - Day
 Liz - Night</t>
         </is>
       </c>
@@ -3047,7 +2953,6 @@
         <is>
           <t>17
 Megan - Day
-David - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3056,7 +2961,7 @@
         <is>
           <t>18
 Megan - Day
-David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3064,19 +2969,19 @@
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>19
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
           <t>20
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 12 - Dr. Amin</t>
+Megan - Day
+Josh - Day
+Britt - Night
+Template Week 10 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -3085,17 +2990,17 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>21
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>22
-Britt - Day
-David - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3104,7 +3009,6 @@
         <is>
           <t>23
 David - Day
-None - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3112,18 +3016,16 @@
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>24
-Kati - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>25
-Kati - Day
-Megan - Day
-Liz - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
@@ -3131,8 +3033,7 @@
         <is>
           <t>26
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
@@ -3140,9 +3041,8 @@
         <is>
           <t>27
 David - Day
-Megan - Day
-Ashley - Night
-Template Week 1</t>
+Liz - Night
+Template Week 11</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -3152,17 +3052,16 @@
         <is>
           <t>28
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>29
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -3170,8 +3069,7 @@
         <is>
           <t>30
 Britt - Day
-Kati - Day
-Liz - Night</t>
+Ashley - Night</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -3258,7 +3156,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>October 2025</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3345,37 +3243,36 @@
       <c r="G4" s="9" t="inlineStr">
         <is>
           <t>1
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>2
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>3
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>4
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 2 - Dr. Amin</t>
+Megan - Day
+Josh  - Day
+Ashley - Night
+Template Week 12 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -3384,35 +3281,34 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>5
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>6
-Britt - Day
-None - Day
-None - Night</t>
+Megan - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>7
-Britt - Day
-None - Day
-None - Night</t>
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>8
-Kati - Day
-None - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3420,8 +3316,8 @@
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>9
-Kati - Day
-None - Day
+David  - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3430,8 +3326,7 @@
         <is>
           <t>10
 David - Day
-None - Day
-None - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
@@ -3439,9 +3334,8 @@
         <is>
           <t>11
 David - Day
-None - Day
-None - Night
-Template Week 3</t>
+Liz - Night
+Template Week 13</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -3451,52 +3345,50 @@
         <is>
           <t>12
 David - Day
-None - Day
-None - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>13
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>14
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>15
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>16
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>17
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3504,10 +3396,10 @@
       <c r="M6" s="9" t="inlineStr">
         <is>
           <t>18
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night
-Template Week 4 - Dr. Amin</t>
+Template Week 14 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -3516,8 +3408,8 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>19
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3525,8 +3417,8 @@
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>20
-Britt - Day
-None - Day
+Megan - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -3535,7 +3427,6 @@
         <is>
           <t>21
 Britt - Day
-None - Day
 Liz - Night</t>
         </is>
       </c>
@@ -3543,8 +3434,8 @@
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>22
-Kati - Day
-None - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3552,8 +3443,8 @@
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>23
-Kati - Day
-David - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -3561,19 +3452,17 @@
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>24
-David - Day
-Megan - Day
-Liz - Night</t>
+David  - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="9" t="inlineStr">
         <is>
           <t>25
-David - Day
-Megan - Day
-Liz - Night
-Template Week 5</t>
+David  - Day
+Josh - Night
+Template Week 1</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -3583,17 +3472,16 @@
         <is>
           <t>26
 David - Day
-Megan - Day
-Liz - Night</t>
+Josh - Night</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>27
-Britt - Day
-None - Day
-Ashley - Night</t>
+David - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -3601,8 +3489,7 @@
         <is>
           <t>28
 Britt - Day
-None - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -3610,8 +3497,8 @@
         <is>
           <t>29
 Megan - Day
-None - Day
-Liz - Night</t>
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
@@ -3619,17 +3506,17 @@
         <is>
           <t>30
 Megan - Day
-David - Day
-Liz - Night</t>
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
           <t>31
-Britt - Day
-Kati - Day
-Ashley - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L8" s="8" t="n"/>
@@ -3711,7 +3598,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>November 2025</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3804,289 +3691,283 @@
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>1
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
+Liz - Night
+Template Week 2 - Dr. Amin</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>3
+Megan - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>4
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>5
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>6
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>7
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>8
+Josh - Day
+Ashley - Night
+Template Week 3</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>9
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>10
+Josh - Day
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>11
+Britt - Day
+David - Night</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>12
+Megan - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>13
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>14
+Megan - Day
+Josh - Day
+David  - Night</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>15
+Megan - Day
+Josh - Day
+David  - Night
+Template Week 4 - Dr. Amin</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>16
+Megan - Day
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>17
+Megan - Day
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>18
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>19
+David - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>20
+David  - Day
+Josh  - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>21
+David - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>22
+David - Day
+Liz - Night
+Template Week 5</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>23
+David  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>24
+David  - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>25
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>26
+Megan - Day
+Josh - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>27
+Megan - Day
+Josh  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>28
+Megan - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>29
+Megan - Day
+Britt  - Day
 Ashley - Night
 Template Week 6 - Dr. Amin</t>
         </is>
       </c>
-      <c r="N4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>2
-Britt - Day
-Kati - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>3
-Megan - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>4
-Megan - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>5
-Kati - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>6
-Kati - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>7
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>8
-David - Day
-None - Day
-Liz - Night
-Template Week 7</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>9
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>10
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>11
-Britt - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>12
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>13
-David - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>14
-Britt - Day
-Kati - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>15
-Britt - Day
-Kati - Day
-None - Night
-Template Week 8 - Dr. Amin</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>16
-Britt - Day
-Kati - Day
-None - Night</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>17
-David - Day
-Britt - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>18
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>19
-Kati - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>20
-Kati - Day
-Megan - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>21
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>22
-David - Day
-None - Day
-Ashley - Night
-Template Week 9</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>23
-David - Day
-None - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>24
-Britt - Day
-None - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>25
-Britt - Day
-Megan - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>26
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>27
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>28
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>29
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 10 - Dr. Amin</t>
-        </is>
-      </c>
       <c r="N8" s="8" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>30
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>31
+Megan - Day
+Britt  - Day
+Liz - Night</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
@@ -4100,7 +3981,7 @@
       <c r="N9" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="A9:B9"/>
@@ -4115,6 +3996,7 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
@@ -4173,7 +4055,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4253,58 +4135,47 @@
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="8" t="n"/>
       <c r="B4" s="8" t="n"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>1
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
+      <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>2
-David - Day
-Megan - Day
-Ashley - Night</t>
+          <t>1
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>3
-Kati - Day
-None - Day
-Liz - Night</t>
+          <t>2
+David - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>4
-Kati - Day
-None - Day
-Liz - Night</t>
+          <t>3
+David  - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>5
-David - Day
-Megan - Day
-Ashley - Night</t>
+          <t>4
+David  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>6
-David - Day
-Megan - Day
-Ashley - Night
-Template Week 11 - Dr. Amin</t>
+          <t>5
+David - Day
+Liz - Night
+Template Week 7 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -4312,65 +4183,61 @@
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>7
-David - Day
-Megan - Day
-Ashley - Night</t>
+          <t>6
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>8
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>7
+David - Day
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>9
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>8
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>10
-Megan - Day
-David - Day
-Ashley - Night</t>
+          <t>9
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>11
-Megan - Day
-David - Day
-Ashley - Night</t>
+          <t>10
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>12
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>11
+Josh - Day
+Britt - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>13
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 12</t>
+          <t>12
+Josh - Day
+Britt  - Day
+Megan - Night
+Template Week 8</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -4378,65 +4245,60 @@
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>14
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>13
+Josh - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>15
-Britt - Day
-David - Day
+          <t>14
+Josh - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>16
-David - Day
-None - Day
-Ashley - Night</t>
+          <t>15
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>17
-Kati - Day
-None - Day
+          <t>16
+David - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>18
-Kati - Day
-Megan - Day
+          <t>17
+David - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>19
-David - Day
-Megan - Day
+          <t>18
+David - Day
 Ashley - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>20
-David - Day
-Megan - Day
+          <t>19
+David - Day
 Ashley - Night
-Template Week 1 - Dr. Amin</t>
+Template Week 9 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -4444,65 +4306,62 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>21
-David - Day
-Megan - Day
+          <t>20
+David - Day
 Ashley - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>22
-Britt - Day
-Kati - Day
+          <t>21
+David - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>23
-Britt - Day
-Kati - Day
+          <t>22
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>24
-David - Day
-None - Day
-None - Night</t>
+          <t>23
+Megan - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>25
-David - Day
-None - Day
-None - Night</t>
+          <t>24
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>26
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>25
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>27
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 2</t>
+          <t>26
+Megan - Day
+Josh - Day
+Britt - Night
+Template Week 10</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -4510,37 +4369,35 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>28
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>27
+Megan - Day
+Josh - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>29
-Britt - Day
-None - Day
-None - Night</t>
+          <t>28
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>30
-Britt - Day
-None - Day
-None - Night</t>
+          <t>29
+David - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>31
-Kati - Day
-None - Day
-Ashley - Night</t>
+          <t>30
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
@@ -4552,7 +4409,7 @@
       <c r="N8" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="38">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C5:D5"/>
@@ -4562,7 +4419,6 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
@@ -4626,7 +4482,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>January 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4715,9 +4571,8 @@
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>1
-Kati - Day
-None - Day
-Ashley - Night</t>
+David - Day
+Josh - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
@@ -4725,8 +4580,7 @@
         <is>
           <t>2
 David - Day
-None - Day
-None - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
@@ -4734,9 +4588,8 @@
         <is>
           <t>3
 David - Day
-None - Day
-None - Night
-Template Week 3 - Dr. Amin</t>
+Liz - Night
+Template Week 11 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -4746,17 +4599,16 @@
         <is>
           <t>4
 David - Day
-None - Day
-None - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>5
-Britt - Day
-Kati - Day
-Liz - Night</t>
+David - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
@@ -4764,34 +4616,32 @@
         <is>
           <t>6
 Britt - Day
-Kati - Day
-Liz - Night</t>
+Ashley - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>7
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>8
-David - Day
-None - Day
-None - Night</t>
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
           <t>9
-Britt - Day
-Kati - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4799,10 +4649,10 @@
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>10
-Britt - Day
-Kati - Day
+Megan - Day
+Josh  - Day
 Ashley - Night
-Template Week 4</t>
+Template Week 12</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -4811,8 +4661,8 @@
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>11
-Britt - Day
-Kati - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4820,8 +4670,8 @@
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>12
-Britt - Day
-None - Day
+Megan - Day
+Britt  - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4829,8 +4679,7 @@
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>13
-Britt - Day
-None - Day
+Britt  - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4838,8 +4687,8 @@
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>14
-Kati - Day
-None - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4847,8 +4696,8 @@
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>15
-Kati - Day
-David - Day
+David  - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4857,7 +4706,6 @@
         <is>
           <t>16
 David - Day
-Megan - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4866,9 +4714,8 @@
         <is>
           <t>17
 David - Day
-Megan - Day
 Liz - Night
-Template Week 5 - Dr. Amin</t>
+Template Week 13 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -4878,7 +4725,6 @@
         <is>
           <t>18
 David - Day
-Megan - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4886,8 +4732,8 @@
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>19
-Britt - Day
-None - Day
+David - Day
+Britt  - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4895,8 +4741,7 @@
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>20
-Britt - Day
-None - Day
+Britt  - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4905,7 +4750,7 @@
         <is>
           <t>21
 Megan - Day
-None - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4914,7 +4759,7 @@
         <is>
           <t>22
 Megan - Day
-David - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4922,8 +4767,8 @@
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>23
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4931,10 +4776,10 @@
       <c r="M7" s="9" t="inlineStr">
         <is>
           <t>24
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night
-Template Week 6</t>
+Template Week 14</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -4943,8 +4788,8 @@
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>25
-Britt - Day
-Kati - Day
+Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4953,7 +4798,7 @@
         <is>
           <t>26
 Megan - Day
-None - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4961,8 +4806,7 @@
       <c r="E8" s="9" t="inlineStr">
         <is>
           <t>27
-Megan - Day
-None - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
@@ -4970,8 +4814,8 @@
       <c r="G8" s="9" t="inlineStr">
         <is>
           <t>28
-Kati - Day
-Megan - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4979,8 +4823,8 @@
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>29
-Kati - Day
-None - Day
+David - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -4988,19 +4832,17 @@
       <c r="K8" s="9" t="inlineStr">
         <is>
           <t>30
-David - Day
-None - Day
-Liz - Night</t>
+David  - Day
+Britt - Night</t>
         </is>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="9" t="inlineStr">
         <is>
           <t>31
-David - Day
-None - Day
-Liz - Night
-Template Week 7 - Dr. Amin</t>
+David  - Day
+Josh - Night
+Template Week 1 - Dr. Amin</t>
         </is>
       </c>
       <c r="N8" s="8" t="n"/>
@@ -5058,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5080,7 +4922,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5162,17 +5004,16 @@
         <is>
           <t>1
 David - Day
-None - Day
-Liz - Night</t>
+Josh - Night</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="9" t="inlineStr">
         <is>
           <t>2
-Britt - Day
-None - Day
-Ashley - Night</t>
+David - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -5180,16 +5021,15 @@
         <is>
           <t>3
 Britt - Day
-None - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="9" t="inlineStr">
         <is>
           <t>4
-David - Day
-None - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5197,28 +5037,28 @@
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>5
-David - Day
-None - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
           <t>6
-Britt - Day
-Kati - Day
-None - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>7
-Britt - Day
-Kati - Day
-None - Night
-Template Week 8 - Dr. Amin</t>
+Megan - Day
+Britt - Day
+Liz - Night
+Template Week 2 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -5227,16 +5067,16 @@
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>8
-Britt - Day
-Kati - Day
-None - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>9
-David - Day
+Megan - Day
 Britt - Day
 Ashley - Night</t>
         </is>
@@ -5245,8 +5085,7 @@
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>10
-David - Day
-None - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5254,8 +5093,7 @@
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>11
-Kati - Day
-None - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -5263,8 +5101,7 @@
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>12
-Kati - Day
-Megan - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -5272,8 +5109,7 @@
       <c r="K5" s="9" t="inlineStr">
         <is>
           <t>13
-David - Day
-Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5281,10 +5117,9 @@
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>14
-David - Day
-None - Day
+Josh - Day
 Ashley - Night
-Template Week 9</t>
+Template Week 3</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -5293,8 +5128,7 @@
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>15
-David - Day
-None - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5302,9 +5136,9 @@
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>16
-Britt - Day
-None - Day
-Liz - Night</t>
+Josh - Day
+Britt - Day
+David - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
@@ -5312,15 +5146,13 @@
         <is>
           <t>17
 Britt - Day
-Megan - Day
-Liz - Night</t>
+David - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>18
-David - Day
 Megan - Day
 Ashley - Night</t>
         </is>
@@ -5329,8 +5161,8 @@
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>19
-David - Day
-Megan - Day
+Megan - Day
+Josh - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5338,19 +5170,19 @@
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>20
-Britt - Day
-Kati - Day
-Liz - Night</t>
+Megan - Day
+Josh - Day
+David  - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
           <t>21
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 10 - Dr. Amin</t>
+Megan - Day
+Josh - Day
+David  - Night
+Template Week 4 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -5359,8 +5191,8 @@
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>22
-Britt - Day
-Kati - Day
+Megan - Day
+Josh - Day
 Liz - Night</t>
         </is>
       </c>
@@ -5368,17 +5200,16 @@
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>23
-David - Day
-Megan - Day
-Ashley - Night</t>
+Megan - Day
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>24
-David - Day
-Megan - Day
+Britt - Day
 Ashley - Night</t>
         </is>
       </c>
@@ -5386,18 +5217,18 @@
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>25
-Kati - Day
-None - Day
-Liz - Night</t>
+David - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>26
-Kati - Day
-None - Day
-Liz - Night</t>
+David  - Day
+Josh  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
@@ -5405,8 +5236,7 @@
         <is>
           <t>27
 David - Day
-Megan - Day
-Ashley - Night</t>
+Liz - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
@@ -5414,15 +5244,43 @@
         <is>
           <t>28
 David - Day
-Megan - Day
-Ashley - Night
-Template Week 11</t>
+Liz - Night
+Template Week 5</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
     </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>29
+David  - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>30
+David  - Day
+Britt - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="38">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C5:D5"/>
@@ -5447,6 +5305,8 @@
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="G4:H4"/>
@@ -5493,7 +5353,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5571,67 +5431,52 @@
       <c r="N3" s="8" t="n"/>
     </row>
     <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>1
-David - Day
-Megan - Day
-Ashley - Night</t>
-        </is>
-      </c>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="8" t="n"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>2
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
+      <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>3
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>1
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>4
-Megan - Day
-David - Day
-Ashley - Night</t>
+          <t>2
+Megan - Day
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>5
-Megan - Day
-David - Day
-Ashley - Night</t>
+          <t>3
+Megan - Day
+Josh  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>6
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>4
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>7
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 12 - Dr. Amin</t>
+          <t>5
+Megan - Day
+Britt  - Day
+Ashley - Night
+Template Week 6 - Dr. Amin</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -5639,65 +5484,61 @@
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>8
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>6
+Megan - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>9
-Britt - Day
-David - Day
-Ashley - Night</t>
+          <t>7
+Megan - Day
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>10
-David - Day
-None - Day
-Ashley - Night</t>
+          <t>8
+Britt  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>11
-Kati - Day
-None - Day
-Liz - Night</t>
+          <t>9
+David - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>12
-Kati - Day
-Megan - Day
-Liz - Night</t>
+          <t>10
+David  - Day
+Josh - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>13
-David - Day
-Megan - Day
-Ashley - Night</t>
+          <t>11
+David  - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>14
-David - Day
-Megan - Day
-Ashley - Night
-Template Week 1</t>
+          <t>12
+David - Day
+Liz - Night
+Template Week 7</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -5705,65 +5546,61 @@
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>15
-David - Day
-Megan - Day
-Ashley - Night</t>
+          <t>13
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>16
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>14
+David - Day
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>17
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>15
+Britt  - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>18
-David - Day
-None - Day
-None - Night</t>
+          <t>16
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>19
-David - Day
-None - Day
-None - Night</t>
+          <t>17
+Josh - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>20
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>18
+Josh - Day
+Britt - Day
+Megan - Night</t>
         </is>
       </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>21
-Britt - Day
-Kati - Day
-Liz - Night
-Template Week 2 - Dr. Amin</t>
+          <t>19
+Josh - Day
+Britt  - Day
+Megan - Night
+Template Week 8 - Dr. Amin</t>
         </is>
       </c>
       <c r="N6" s="8" t="n"/>
@@ -5771,65 +5608,60 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>22
-Britt - Day
-Kati - Day
-Liz - Night</t>
+          <t>20
+Josh - Day
+Britt  - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>23
-Britt - Day
-None - Day
-None - Night</t>
+          <t>21
+Josh - Day
+Britt - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>24
-Britt - Day
-None - Day
-None - Night</t>
+          <t>22
+Britt - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>25
-Kati - Day
-None - Day
-Ashley - Night</t>
+          <t>23
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>26
-Kati - Day
-None - Day
-Ashley - Night</t>
+          <t>24
+David - Day
+Liz - Night</t>
         </is>
       </c>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>27
-David - Day
-None - Day
-None - Night</t>
+          <t>25
+David - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>28
-David - Day
-None - Day
-None - Night
-Template Week 3</t>
+          <t>26
+David - Day
+Ashley - Night
+Template Week 9</t>
         </is>
       </c>
       <c r="N7" s="8" t="n"/>
@@ -5837,34 +5669,45 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>29
-David - Day
-None - Day
-None - Night</t>
+          <t>27
+David - Day
+Ashley - Night</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>30
-Britt - Day
-Kati - Day
+          <t>28
+David - Day
+Britt - Day
 Liz - Night</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
+          <t>29
+Britt - Day
+Liz - Night</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>30
+Megan - Day
+Ashley - Night</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
           <t>31
-Britt - Day
-Kati - Day
-Liz - Night</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
+Megan - Day
+Josh - Day
+Ashley - Night</t>
+        </is>
+      </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
@@ -5879,9 +5722,9 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
@@ -5898,9 +5741,9 @@
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="K7:L7"/>
